--- a/data/homes2.xlsx
+++ b/data/homes2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ATS\crm_bunyodkorhouse\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41A23067-800B-48DF-91E4-ED1135FBE1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B98100E-ED8E-4D75-AF58-F36BEEC80886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{91816ED0-98EA-49CB-8BA6-28DEB5D24487}"/>
   </bookViews>
@@ -555,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{808DFD91-5F06-4417-9E59-F42975424D87}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -1346,6 +1346,74 @@
         <v>7000000</v>
       </c>
     </row>
+    <row r="47" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="10">
+        <v>-1</v>
+      </c>
+      <c r="B47" s="5">
+        <v>95</v>
+      </c>
+      <c r="C47" s="5">
+        <v>59</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2</v>
+      </c>
+      <c r="E47" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="10">
+        <v>-1</v>
+      </c>
+      <c r="B48" s="5">
+        <v>96</v>
+      </c>
+      <c r="C48" s="5">
+        <v>59</v>
+      </c>
+      <c r="D48" s="5">
+        <v>2</v>
+      </c>
+      <c r="E48" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="10">
+        <v>-1</v>
+      </c>
+      <c r="B49" s="5">
+        <v>97</v>
+      </c>
+      <c r="C49" s="5">
+        <v>59</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2</v>
+      </c>
+      <c r="E49" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="10">
+        <v>-1</v>
+      </c>
+      <c r="B50" s="5">
+        <v>98</v>
+      </c>
+      <c r="C50" s="5">
+        <v>59</v>
+      </c>
+      <c r="D50" s="5">
+        <v>2</v>
+      </c>
+      <c r="E50" s="5">
+        <v>7000000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
